--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -749,31 +749,33 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="22" t="str">
+      <c r="A2" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B2" s="22">
         <f>IF(A2&lt;&gt;"",1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="1">
         <f t="shared" ref="D2:D18" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
+        <v>1400</v>
+      </c>
+      <c r="E2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
+        <v>401.03124158893064</v>
+      </c>
+      <c r="F2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
+        <v>998.9687584110693</v>
+      </c>
+      <c r="G2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
-        <v/>
-      </c>
-      <c r="H2" s="1" t="str">
+        <v>19001.031241588931</v>
+      </c>
+      <c r="H2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
-        <v/>
+        <v>998.96875841106885</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>17</v>
@@ -1116,7 +1118,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1151,7 +1153,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>23800</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1186,7 +1188,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>23800</v>
+        <v>19001.031241588931</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1221,7 +1223,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>0</v>
+        <v>998.96875841106885</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1254,9 +1256,9 @@
       <c r="J16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="16" t="str">
+      <c r="K16" s="16">
         <f>IF(A2,A2, "")</f>
-        <v/>
+        <v>46204</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1289,9 +1291,9 @@
       <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="18" t="str">
+      <c r="K17" s="18">
         <f xml:space="preserve"> IF(A2,(K16 + (17*7)),"")</f>
-        <v/>
+        <v>46323</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -791,31 +791,33 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="23" t="str">
+      <c r="A3" s="19">
+        <v>46211</v>
+      </c>
+      <c r="B3" s="23">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>381.00035751422342</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>1018.9996424857766</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>17982.031599103153</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>2017.968400896847</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>10</v>
@@ -1118,7 +1120,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1153,7 +1155,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>22400</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1188,7 +1190,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>19001.031241588931</v>
+        <v>17982.031599103153</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1223,7 +1225,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>998.96875841106885</v>
+        <v>2017.968400896847</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -827,31 +827,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>360.56782292398606</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>1039.4321770760139</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>16942.599422027139</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>3057.4005779728614</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -859,31 +861,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
+      <c r="A5" s="19">
+        <v>46225</v>
+      </c>
+      <c r="B5" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>339.7255840979721</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>1060.2744159020278</v>
+      </c>
+      <c r="G5" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>15882.325006125111</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>4117.674993874889</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -1120,7 +1124,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1155,7 +1159,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>21000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1190,7 +1194,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>17982.031599103153</v>
+        <v>15882.325006125111</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1225,7 +1229,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2017.968400896847</v>
+        <v>4117.674993874889</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -895,31 +895,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
+      <c r="A6" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>318.4654258262637</v>
+      </c>
+      <c r="F6" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
+        <v>1081.5345741737362</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>14800.790431951375</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>5199.2095680486254</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -927,31 +929,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46239</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>296.77896817115123</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>1103.2210318288487</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>13697.569400122526</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>6302.4305998774744</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1124,7 +1128,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>18200</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1194,7 +1198,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>15882.325006125111</v>
+        <v>13697.569400122526</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1229,7 +1233,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4117.674993874889</v>
+        <v>6302.4305998774744</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -965,31 +965,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
+      <c r="A8" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>274.657663164084</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
+        <v>1125.3423368359161</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>12572.227063286609</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>7427.7729367133907</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1000,31 +1002,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46253</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>252.09279143638921</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>1147.9072085636108</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>11424.319854722999</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>8575.6801452770014</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1128,7 +1132,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1198,7 +1202,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Y_Seema_Weekly.xlsx
@@ -1038,31 +1038,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
+      <c r="A10" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B10" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>229.07545878243178</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
+        <v>1170.9245412175683</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>10253.395313505431</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>9746.6046864945693</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1072,67 +1074,71 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
+      <c r="A11" s="19">
+        <v>46267</v>
+      </c>
+      <c r="B11" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>205.59659265386028</v>
+      </c>
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
+        <v>1194.4034073461398</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>9058.9919061592918</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>10941.008093840708</v>
       </c>
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
+      <c r="A12" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B12" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>181.6469385835567</v>
+      </c>
+      <c r="F12" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
+        <v>1218.3530614164433</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>7840.638844742849</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>12159.361155257151</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1167,7 +1173,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>12600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1202,7 +1208,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>11424.319854722999</v>
+        <v>7840.638844742849</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1237,7 +1243,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>8575.6801452770014</v>
+        <v>12159.361155257151</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
